--- a/Excel+LAB+4+Dataset_Dmart.xlsx
+++ b/Excel+LAB+4+Dataset_Dmart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/401b4826a347cf2b/Desktop/DMART Sales Analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="11_DA76F9DC5DE57EA3DCE059A5D841EB70A2461B6F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F6FD552-9093-45E9-A4A9-D82EAA82575E}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="11_DA76F9DC5DE57EA3DCE059A5D841EB70A2461B6F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D45C2804-2363-44F7-9DBE-8373CCFCA2FC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1679,7 +1679,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -1869,18 +1869,18 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1904,17 +1904,17 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
-        <right/>
+        <right style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </right>
         <top style="thin">
           <color theme="4" tint="0.39994506668294322"/>
         </top>
         <bottom style="thin">
           <color theme="4" tint="0.39994506668294322"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1947,54 +1947,6 @@
         </bottom>
         <vertical/>
         <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </right>
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -2126,7 +2078,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
+      <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -2155,7 +2107,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
+      <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right/>
@@ -2324,6 +2276,36 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color theme="4" tint="0.39994506668294322"/>
@@ -2334,6 +2316,48 @@
         </top>
         <bottom style="thin">
           <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
         </bottom>
       </border>
     </dxf>
@@ -2372,30 +2396,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Table Style 1" pivot="0" count="0" xr9:uid="{76349F9B-9EB8-4FB6-BC06-FDD4E22F9B3B}"/>
@@ -2412,25 +2412,29 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2DA19D26-7B8B-4964-A276-2367208F00EB}" name="DMART_SALES_DATASET" displayName="DMART_SALES_DATASET" ref="A1:O499" totalsRowShown="0" headerRowDxfId="16" dataDxfId="2" headerRowBorderDxfId="18" tableBorderDxfId="19" totalsRowBorderDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2DA19D26-7B8B-4964-A276-2367208F00EB}" name="DMART_SALES_DATASET" displayName="DMART_SALES_DATASET" ref="A1:O499" totalsRowShown="0" headerRowDxfId="19" dataDxfId="17" headerRowBorderDxfId="18" tableBorderDxfId="16" totalsRowBorderDxfId="15">
   <autoFilter ref="A1:O499" xr:uid="{2DA19D26-7B8B-4964-A276-2367208F00EB}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{D4537C2F-3D88-447D-8E1B-7D3EAD24920E}" name="Column1" dataDxfId="15"/>
-    <tableColumn id="15" xr3:uid="{BAAC444F-2856-4A9E-B100-BF35A42CC9FB}" name="Updated_Region" dataDxfId="0"/>
-    <tableColumn id="2" xr3:uid="{72A4A585-D368-4B6D-A5AF-FD30BA63455E}" name="Region" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{8FE180AB-F0DE-4F63-A551-9FB6D48DDED6}" name="Category" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{F816A267-F3DB-4375-892D-F3EB982E68CE}" name="sales" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{9EAFE75A-D9CE-422B-921B-8E40B7C46712}" name="discount" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{0F81F223-2A6D-4A16-8DF0-BB8CCDF1D968}" name="quantity" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{FA7FEC0A-64E2-407C-BDEC-80668FC23A18}" name="order_date" dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{F2ADF858-C4B5-4F5B-882B-9952705D721F}" name="delivery_date" dataDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{CA263EFE-CD9C-4CA0-9180-D1C76CF55699}" name="customer_type" dataDxfId="7"/>
-    <tableColumn id="10" xr3:uid="{1550D2BB-F8E7-494E-9BE3-167C8B70FE68}" name="customer_type2" dataDxfId="6"/>
-    <tableColumn id="11" xr3:uid="{45DE1469-0AEC-4B81-B3C1-C472609F9E82}" name="payment_mode" dataDxfId="5"/>
-    <tableColumn id="12" xr3:uid="{CE9812C3-ED21-44EA-A50E-F3E465DC18DE}" name="profit" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{D4537C2F-3D88-447D-8E1B-7D3EAD24920E}" name="Column1" dataDxfId="14"/>
+    <tableColumn id="15" xr3:uid="{BAAC444F-2856-4A9E-B100-BF35A42CC9FB}" name="Updated_Region" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{72A4A585-D368-4B6D-A5AF-FD30BA63455E}" name="Region" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{8FE180AB-F0DE-4F63-A551-9FB6D48DDED6}" name="Category" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{F816A267-F3DB-4375-892D-F3EB982E68CE}" name="sales" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{9EAFE75A-D9CE-422B-921B-8E40B7C46712}" name="discount" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{0F81F223-2A6D-4A16-8DF0-BB8CCDF1D968}" name="quantity" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{FA7FEC0A-64E2-407C-BDEC-80668FC23A18}" name="order_date" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{F2ADF858-C4B5-4F5B-882B-9952705D721F}" name="delivery_date" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{CA263EFE-CD9C-4CA0-9180-D1C76CF55699}" name="customer_type" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{1550D2BB-F8E7-494E-9BE3-167C8B70FE68}" name="customer_type2" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{45DE1469-0AEC-4B81-B3C1-C472609F9E82}" name="payment_mode" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{CE9812C3-ED21-44EA-A50E-F3E465DC18DE}" name="profit" dataDxfId="2"/>
     <tableColumn id="14" xr3:uid="{BE56AE36-70A6-49BE-AD72-3C8E477287FB}" name="Updated_City_Names" dataDxfId="1"/>
-    <tableColumn id="13" xr3:uid="{D2E128A5-9076-4C85-8041-64A9821A5F97}" name="city" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{D2E128A5-9076-4C85-8041-64A9821A5F97}" name="city" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight17" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2638,7 +2642,8 @@
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.6640625" customWidth="1"/>
-    <col min="2" max="3" width="12.109375" customWidth="1"/>
+    <col min="2" max="2" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" customWidth="1"/>
     <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="11.77734375" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
